--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
@@ -989,7 +989,7 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>**保険料の算式チェーンは第9期の実数で検算した。**標準給付費3,566,486千円を入れると月額6,442円となり、実際の6,600円に対して2.4％の差にとどまる（差は地域支援事業費・調整交付金見込額・被保険者数を仮置きしたことによる）。算式そのものは通っている。</t>
+          <t>**保険料の算式チェーンは第9期の実数で検算した。**標準給付費3,566,486千円を入れると月額6,865円となり、第9期計画の算定値6,886円（基金取崩前）に対して0.3％の差にとどまる。**令和8年9月28日、調整交付金見込額の基数に総合事業費を加える訂正を行い、この検算の差は6.4％から0.3％に縮んだ。**算式そのものは通っている。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
@@ -989,7 +989,7 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>**保険料の算式チェーンは第9期の実数で検算した。**標準給付費3,566,486千円を入れると月額6,865円となり、第9期計画の算定値6,886円（基金取崩前）に対して0.3％の差にとどまる。**令和8年9月28日、調整交付金見込額の基数に総合事業費を加える訂正を行い、この検算の差は6.4％から0.3％に縮んだ。**算式そのものは通っている。</t>
+          <t>**保険料の算式チェーンは第9期の実数で検算した。**標準給付費3,566,486千円を入れると月額6,865円となり、第9期計画の算定値6,886円（基金取崩前）に対して0.3％の差にとどまる。**調整交付金見込額の基数は、調整交付金相当額（5％）と同じ（標準給付費＋総合事業費）とし、見える化システムの出力と1円まで照合してある。**算式そのものは通っている。</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>**ケース設定をC1〜C6に組み直した（標準低位・標準高位・施設整備あり・制度改正の影響・基金活用・保険料据置の逆算）。**引継ぎ時点の3ケースは基金の扱いのみで、仕様書が例示する「施設整備」「制度改正」に対応していなかった。算式は第9期の実数で検算済み（6,442円 対 実際6,600円。仮置き値ぶんの差）</t>
+          <t>**ケース設定をC1〜C6に組み直した（標準低位・標準高位・施設整備あり・制度改正の影響・基金活用・保険料据置の逆算）。**引継ぎ時点の3ケースは基金の扱いのみで、仕様書が例示する「施設整備」「制度改正」に対応していなかった。算式は第9期の実数で検算済み（6,865円 対 計画の算定値6,886円。差0.3％）</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
@@ -933,7 +933,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>令和7年度調査の結果報告書を受領し、集計データを整理した。**在宅の要介護認定者の42.1％がサービスを利用しておらず、その理由の92.9％が需要側の要因（状態ではない46.8％、本人の希望なし29.2％、家族が介護16.9％）で、供給制約は0.6％であった。**これにより第10期の施策方向を、供給確保から認定運用の確認・利用意向への働きかけ・レスパイトへ組み替える。</t>
+          <t>令和7年度調査の結果報告書を受領し、集計データを整理した。**在宅の要介護認定者の42.1％がサービスを利用しておらず、その理由の上位3つは需要側のもの（状態ではない46.8％、本人の希望なし29.2％、家族が介護16.9％）で、供給側の理由を挙げた方は1人であった。**これにより第10期の施策方向を、供給確保から認定運用の確認・利用意向への働きかけ・レスパイトへ組み替える。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
@@ -4432,7 +4432,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>**逆算表を作成済み（令和9年2月下旬の校了が動かせない期限）。**12月までに印刷業者を押さえる必要がある</t>
+          <t>**逆算表を作成済み（令和9年2月下旬の校了が動かせない期限）。**年度末は印刷が集中するため1月中に業者を押さえる必要がある</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">

--- a/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/12_進捗管理/小野町_計画策定業務_進捗管理表_20260813.xlsx
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>介護保険財政整理ブック（D47・D48系25指標、H26〜R5）。繰越金182.0百万円・基金純増88.1百万円</t>
+          <t>介護保険財政整理ブック（D47・D48系25指標、H26〜R5）。繰越金182.0百万円・基金残高120.0百万円（令和5年度末・町の財務書類）</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>繰越金182.0百万円（保険給付費の16.5%）、基金純増88.1百万円。保険料6,600円に対し必要保険料6,131円</t>
+          <t>繰越金182.0百万円（保険給付費の16.5%）、基金残高120.0百万円（令和5年度末）。保険料6,600円に対し必要保険料6,131円</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
